--- a/test/技术工单/输入附件-扩展版.xlsx
+++ b/test/技术工单/输入附件-扩展版.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="issues" sheetId="1" r:id="R9d369150a6bf4380"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="activity" sheetId="2" r:id="R2d439c4b3034415e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="issues" sheetId="1" r:id="R7933c377e0c44df2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="activity" sheetId="2" r:id="Re49cc390aac04d1f"/>
   </x:sheets>
 </x:workbook>
 </file>
